--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DFS_HRM-2031-0432/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -460,72 +460,72 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.7735</v>
+        <v>16.97666</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62105</v>
+        <v>16.73398</v>
       </c>
       <c r="E2" t="n">
-        <v>17.01931</v>
+        <v>16.78519</v>
       </c>
       <c r="F2" t="n">
-        <v>42.67789</v>
+        <v>41.56233</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05083</v>
+        <v>0.05218</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86328</v>
+        <v>1.85558</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.09811</v>
+        <v>16.97825</v>
       </c>
       <c r="D3" t="n">
-        <v>16.58254</v>
+        <v>16.72878</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64921</v>
+        <v>16.96718</v>
       </c>
       <c r="F3" t="n">
-        <v>43.35465</v>
+        <v>42.15594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05179</v>
+        <v>0.05146</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86385</v>
+        <v>1.81262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.3078</v>
+        <v>16.94219</v>
       </c>
       <c r="D4" t="n">
-        <v>16.69564</v>
+        <v>16.76057</v>
       </c>
       <c r="E4" t="n">
-        <v>16.96231</v>
+        <v>16.80451</v>
       </c>
       <c r="F4" t="n">
-        <v>44.17773</v>
+        <v>41.88018</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05118</v>
+        <v>0.05105</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86054</v>
+        <v>1.84393</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.71815</v>
+        <v>17.17993</v>
       </c>
       <c r="D5" t="n">
-        <v>16.5367</v>
+        <v>16.56943</v>
       </c>
       <c r="E5" t="n">
-        <v>16.79729</v>
+        <v>16.6943</v>
       </c>
       <c r="F5" t="n">
-        <v>43.15138</v>
+        <v>43.4188</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05175</v>
+        <v>0.0511</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84081</v>
+        <v>1.78319</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.83264</v>
+        <v>16.96354</v>
       </c>
       <c r="D6" t="n">
-        <v>16.82039</v>
+        <v>16.61799</v>
       </c>
       <c r="E6" t="n">
-        <v>16.7048</v>
+        <v>16.69886</v>
       </c>
       <c r="F6" t="n">
-        <v>43.46906</v>
+        <v>44.25295</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0506</v>
+        <v>0.0515</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84071</v>
+        <v>1.88788</v>
       </c>
     </row>
     <row r="7">
@@ -585,493 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.1406</v>
+        <v>17.02908</v>
       </c>
       <c r="D7" t="n">
-        <v>16.8409</v>
+        <v>16.5172</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66953</v>
+        <v>16.92663</v>
       </c>
       <c r="F7" t="n">
-        <v>41.93734</v>
+        <v>43.45821</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04998</v>
+        <v>0.05061</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85799</v>
+        <v>1.83905</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.9221</v>
+        <v>17.4184</v>
       </c>
       <c r="D8" t="n">
-        <v>17.12289</v>
+        <v>16.89742</v>
       </c>
       <c r="E8" t="n">
-        <v>16.87664</v>
+        <v>17.32537</v>
       </c>
       <c r="F8" t="n">
-        <v>42.94477</v>
+        <v>42.496</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05127</v>
+        <v>0.05094</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82176</v>
+        <v>1.83998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.13815</v>
+        <v>17.08775</v>
       </c>
       <c r="D9" t="n">
-        <v>16.58627</v>
+        <v>16.63553</v>
       </c>
       <c r="E9" t="n">
-        <v>16.76616</v>
+        <v>16.85663</v>
       </c>
       <c r="F9" t="n">
-        <v>42.27581</v>
+        <v>43.40683</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05046</v>
+        <v>0.05055</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82974</v>
+        <v>1.81856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.79389</v>
+        <v>16.97943</v>
       </c>
       <c r="D10" t="n">
-        <v>16.59733</v>
+        <v>16.64363</v>
       </c>
       <c r="E10" t="n">
-        <v>17.06485</v>
+        <v>16.84225</v>
       </c>
       <c r="F10" t="n">
-        <v>42.79066</v>
+        <v>42.88333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05121</v>
+        <v>0.05143</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84832</v>
+        <v>1.86149</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.22896</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.6469</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.89475</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.60101</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.86099</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.03419</v>
+        <v>17.03509</v>
       </c>
       <c r="D12" t="n">
-        <v>16.77336</v>
+        <v>16.74794</v>
       </c>
       <c r="E12" t="n">
-        <v>16.95064</v>
+        <v>17.0327</v>
       </c>
       <c r="F12" t="n">
-        <v>42.87985</v>
+        <v>43.03093</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05118</v>
+        <v>0.05135</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82747</v>
+        <v>1.85392</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.06114</v>
+        <v>17.08297</v>
       </c>
       <c r="D13" t="n">
-        <v>16.84708</v>
+        <v>16.83152</v>
       </c>
       <c r="E13" t="n">
-        <v>16.61114</v>
+        <v>16.96372</v>
       </c>
       <c r="F13" t="n">
-        <v>43.56542</v>
+        <v>42.56218</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05063</v>
+        <v>0.04952</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83429</v>
+        <v>1.83796</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.29872</v>
+        <v>17.034</v>
       </c>
       <c r="D14" t="n">
-        <v>16.51831</v>
+        <v>16.76848</v>
       </c>
       <c r="E14" t="n">
-        <v>17.02822</v>
+        <v>16.94132</v>
       </c>
       <c r="F14" t="n">
-        <v>42.97852</v>
+        <v>43.41503</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05162</v>
+        <v>0.0504</v>
       </c>
       <c r="H14" t="n">
-        <v>1.83103</v>
+        <v>1.87295</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.32068</v>
+        <v>17.24508</v>
       </c>
       <c r="D15" t="n">
-        <v>16.95547</v>
+        <v>16.82458</v>
       </c>
       <c r="E15" t="n">
-        <v>16.94924</v>
+        <v>17.07386</v>
       </c>
       <c r="F15" t="n">
-        <v>43.15117</v>
+        <v>43.07538</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0512</v>
+        <v>0.05128</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82174</v>
+        <v>1.81476</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.2409</v>
+        <v>17.12776</v>
       </c>
       <c r="D16" t="n">
-        <v>16.65693</v>
+        <v>16.75769</v>
       </c>
       <c r="E16" t="n">
-        <v>16.76474</v>
+        <v>16.83238</v>
       </c>
       <c r="F16" t="n">
-        <v>43.36987</v>
+        <v>43.69099</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0511</v>
+        <v>0.05034</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81617</v>
+        <v>1.83832</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.80299</v>
+        <v>17.01018</v>
       </c>
       <c r="D17" t="n">
-        <v>16.7265</v>
+        <v>16.85637</v>
       </c>
       <c r="E17" t="n">
-        <v>16.87505</v>
+        <v>16.99557</v>
       </c>
       <c r="F17" t="n">
-        <v>43.64842</v>
+        <v>43.53379</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05042</v>
+        <v>0.05171</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85304</v>
+        <v>1.81813</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.75911</v>
+        <v>16.97563</v>
       </c>
       <c r="D18" t="n">
-        <v>16.77948</v>
+        <v>16.86616</v>
       </c>
       <c r="E18" t="n">
-        <v>16.61902</v>
+        <v>16.87439</v>
       </c>
       <c r="F18" t="n">
-        <v>43.34624</v>
+        <v>42.48755</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05027</v>
+        <v>0.05103</v>
       </c>
       <c r="H18" t="n">
-        <v>1.86049</v>
+        <v>1.83472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.8472</v>
+        <v>17.10235</v>
       </c>
       <c r="D19" t="n">
-        <v>16.95935</v>
+        <v>16.82781</v>
       </c>
       <c r="E19" t="n">
-        <v>16.43555</v>
+        <v>17.03991</v>
       </c>
       <c r="F19" t="n">
-        <v>43.9053</v>
+        <v>42.19041</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05139</v>
+        <v>0.05138</v>
       </c>
       <c r="H19" t="n">
-        <v>1.78765</v>
+        <v>1.85586</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.16868</v>
+        <v>17.12356</v>
       </c>
       <c r="D20" t="n">
-        <v>17.03904</v>
+        <v>16.90314</v>
       </c>
       <c r="E20" t="n">
-        <v>16.96507</v>
+        <v>16.99866</v>
       </c>
       <c r="F20" t="n">
-        <v>42.76375</v>
+        <v>42.76042</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05031</v>
+        <v>0.05153</v>
       </c>
       <c r="H20" t="n">
-        <v>1.85925</v>
+        <v>1.8491</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>16.98337</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.44976</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.81611</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.77508</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.86504</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.62508</v>
+        <v>17.10928</v>
       </c>
       <c r="D22" t="n">
-        <v>1.12935</v>
+        <v>16.64987</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.9837</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42.33964</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.82376</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.61353</v>
+        <v>16.99536</v>
       </c>
       <c r="D23" t="n">
-        <v>1.15388</v>
+        <v>16.82356</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.84491</v>
+      </c>
+      <c r="F23" t="n">
+        <v>44.31945</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.88263</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 23</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.59898</v>
+        <v>17.19328</v>
       </c>
       <c r="D24" t="n">
-        <v>1.13639</v>
+        <v>16.83867</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.94834</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.21699</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.86961</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 24</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.61969</v>
+        <v>16.92935</v>
       </c>
       <c r="D25" t="n">
-        <v>1.13887</v>
+        <v>16.8685</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.89431</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42.98143</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.82286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.6086</v>
+        <v>16.91097</v>
       </c>
       <c r="D26" t="n">
-        <v>1.12207</v>
+        <v>16.55175</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.90805</v>
+      </c>
+      <c r="F26" t="n">
+        <v>43.27251</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05114</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.837</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.62493</v>
+        <v>17.05496</v>
       </c>
       <c r="D27" t="n">
-        <v>1.11243</v>
+        <v>16.68899</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.88682</v>
+      </c>
+      <c r="F27" t="n">
+        <v>43.69722</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.88566</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.61252</v>
+        <v>16.98896</v>
       </c>
       <c r="D28" t="n">
-        <v>1.12426</v>
+        <v>16.8459</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.94248</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.55452</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05182</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.80802</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 28</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.59932</v>
+        <v>16.74372</v>
       </c>
       <c r="D29" t="n">
-        <v>1.10947</v>
+        <v>16.67827</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.71705</v>
+      </c>
+      <c r="F29" t="n">
+        <v>42.62388</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05121</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.8275</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.98438</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.87195</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.91428</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.16699</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.82928</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>17.09219</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.85242</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.85799</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42.5985</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05105</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.8305</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.92538</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.7238</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.85196</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42.70992</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.05142</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.8259</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.04423</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.48799</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.02965</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.78414</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.85006</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.15416</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.60448</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.76025</v>
+      </c>
+      <c r="F34" t="n">
+        <v>40.986</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05106</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.79717</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.9268</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.74592</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.91384</v>
+      </c>
+      <c r="F35" t="n">
+        <v>42.5746</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.82036</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.08946</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.41351</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.84606</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42.948</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.85422</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.04604</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.49948</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.02263</v>
+      </c>
+      <c r="F37" t="n">
+        <v>42.23372</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05112</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.8571</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.68624</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.07635</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.63281</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.0709</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.25162</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.92064</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.23928</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.43876</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.96748</v>
+      </c>
+      <c r="G40" t="n">
+        <v>35.03053</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.60803</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.14775</v>
+      <c r="C41" t="n">
+        <v>17.01071</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16.3695</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.55126</v>
+      </c>
+      <c r="F41" t="n">
+        <v>21.78346</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34.98892</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.94337</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.30349</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.86682</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.62812</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.19782</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.85305</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.19882</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.58391</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.09632</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.87669</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.90173</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.16623</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.5805</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.79043</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.35259</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.00422</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.2101</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.95392</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.60032</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.73629</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.2294</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.3808</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.52558</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.14907</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.35476</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.89961</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15.95242</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.47455</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.76365</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.30433</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>16.72088</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.28972</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.52199</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.1777</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.36156</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.96735</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.07941</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.64425</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.17606</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.82342</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.86868</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.11814</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.78982</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.56995</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.57127</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.6281</v>
+      </c>
+      <c r="D51" t="n">
+        <v>15.9938</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.3244</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22.31823</v>
+      </c>
+      <c r="G51" t="n">
+        <v>35.10916</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.92393</v>
+      </c>
+      <c r="D52" t="n">
+        <v>15.96238</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.35705</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.97577</v>
+      </c>
+      <c r="G52" t="n">
+        <v>34.46405</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.64762</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.17284</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.52458</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.79384</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.81315</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.04989</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.33891</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.37013</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.08605</v>
+      </c>
+      <c r="G54" t="n">
+        <v>35.1251</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.70889</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.10297</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.57837</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22.52149</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.87588</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17.03703</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.06236</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.72775</v>
+      </c>
+      <c r="F56" t="n">
+        <v>22.40095</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.14701</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17.05471</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.07058</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.87956</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22.30138</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35.06237</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.78919</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.00651</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.72032</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22.06091</v>
+      </c>
+      <c r="G58" t="n">
+        <v>34.59369</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.29312</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.40264</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.51279</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22.11931</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.38935</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.95658</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.18696</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.76263</v>
+      </c>
+      <c r="F60" t="n">
+        <v>21.71178</v>
+      </c>
+      <c r="G60" t="n">
+        <v>35.21857</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>17.13767</v>
+      </c>
+      <c r="D61" t="n">
+        <v>16.14885</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.83475</v>
+      </c>
+      <c r="F61" t="n">
+        <v>22.2987</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.34051</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>16.87205</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15.95198</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.73186</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22.18264</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.55953</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>16.90916</v>
+      </c>
+      <c r="D63" t="n">
+        <v>15.87504</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.68785</v>
+      </c>
+      <c r="F63" t="n">
+        <v>21.78361</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.12505</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>16.91084</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.2709</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.62222</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.90966</v>
+      </c>
+      <c r="G64" t="n">
+        <v>34.37107</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>16.54056</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16.23528</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.47247</v>
+      </c>
+      <c r="F65" t="n">
+        <v>21.88515</v>
+      </c>
+      <c r="G65" t="n">
+        <v>35.26987</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16.79274</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.17806</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.68477</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22.31554</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.86562</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>16.75141</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16.27482</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.74175</v>
+      </c>
+      <c r="F67" t="n">
+        <v>22.30087</v>
+      </c>
+      <c r="G67" t="n">
+        <v>34.0797</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16.97352</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.10788</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.22059</v>
+      </c>
+      <c r="F68" t="n">
+        <v>21.53412</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.34835</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16.98619</v>
+      </c>
+      <c r="D69" t="n">
+        <v>15.58868</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.5074</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21.90443</v>
+      </c>
+      <c r="G69" t="n">
+        <v>34.91661</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16.96425</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16.05183</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.7167</v>
+      </c>
+      <c r="F70" t="n">
+        <v>21.6815</v>
+      </c>
+      <c r="G70" t="n">
+        <v>34.61255</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>16.91753</v>
+      </c>
+      <c r="D71" t="n">
+        <v>16.26839</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.59595</v>
+      </c>
+      <c r="F71" t="n">
+        <v>22.19997</v>
+      </c>
+      <c r="G71" t="n">
+        <v>35.29531</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.77182</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16.2431</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.4317</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.95835</v>
+      </c>
+      <c r="G72" t="n">
+        <v>34.74669</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.92962</v>
+      </c>
+      <c r="D73" t="n">
+        <v>16.17562</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.34475</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.63747</v>
+      </c>
+      <c r="G73" t="n">
+        <v>34.1924</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.8252</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16.01856</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.50903</v>
+      </c>
+      <c r="F74" t="n">
+        <v>22.01587</v>
+      </c>
+      <c r="G74" t="n">
+        <v>34.01351</v>
       </c>
     </row>
   </sheetData>
